--- a/docs/EXPOSURE_CONTRACT_REVIEW_2026-07-28.xlsx
+++ b/docs/EXPOSURE_CONTRACT_REVIEW_2026-07-28.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF9999"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FF9999"/>
       </patternFill>
     </fill>
   </fills>
@@ -936,7 +936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>CURRENT VALUE</t>
+          <t>RULED VALUE</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>RULED VALUE</t>
+          <t>STATUS</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
@@ -1044,7 +1044,11 @@
           <t>you can have 2-4 strength days (depending on preference and availability)</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -1092,7 +1096,11 @@
           <t>you can have 2-4 strength days (depending on preference and availability)</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -1140,7 +1148,11 @@
           <t>you can have 2-4 strength days (depending on preference and availability)</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -1188,7 +1200,11 @@
           <t>How many conditioning exposures per week: 3-5 depending on phase of year</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Value is an expression, not a literal — it varies with the athlete's anchors. Ruling it means ruling the EXPRESSION, or replacing it with a fixed number.</t>
@@ -1236,7 +1252,11 @@
           <t>How many conditioning exposures per week: 3-5 depending on phase of year</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Value is an expression, not a literal — it varies with the athlete's anchors. Ruling it means ruling the EXPRESSION, or replacing it with a fixed number.</t>
@@ -1284,7 +1304,11 @@
           <t>How many conditioning exposures per week: 3-5 depending on phase of year</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Value is an expression, not a literal — it varies with the athlete's anchors. Ruling it means ruling the EXPRESSION, or replacing it with a fixed number.</t>
@@ -1332,7 +1356,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -1380,7 +1408,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -1428,7 +1460,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -1463,7 +1499,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1476,7 +1512,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -1511,7 +1551,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1524,7 +1564,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -1559,7 +1603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1572,7 +1616,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -1607,7 +1655,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1620,10 +1668,14 @@
           <t>How many hard days per week max: 4</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 states a hard-day max of 4.</t>
+          <t>RULED and amended into Bible S2: prefer 4 hard days, permit 5, unit is DAYS. Doubling up is ONE hard day and two hard sessions, free against the budget. Easy/long-slow never counts. A 6th hard day is refused with plain copy. Bye-recovery and early off-season keep the lower 2/4.</t>
         </is>
       </c>
     </row>
@@ -1653,9 +1705,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>bible_conflict</t>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1668,10 +1720,14 @@
           <t>How many hard days per week max: 4</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 states a hard-DAY max of 4. This permits 5. Also the unit question: the Bible counts DAYS ("6 sessions ... spread over 3-4 days"), the engine spends this on SESSIONS. Batch 3 owns the unit; this cell owns the number.</t>
+          <t>RULED and amended into Bible S2: prefer 4 hard days, permit 5, unit is DAYS. Doubling up is ONE hard day and two hard sessions, free against the budget. Easy/long-slow never counts. A 6th hard day is refused with plain copy. Bye-recovery and early off-season keep the lower 2/4.</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1772,11 @@
           <t>you can have 2-4 strength days (depending on preference and availability)</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -1764,7 +1824,11 @@
           <t>you can have 2-4 strength days (depending on preference and availability)</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -1812,7 +1876,11 @@
           <t>you can have 2-4 strength days (depending on preference and availability)</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -1845,9 +1913,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1860,10 +1928,14 @@
           <t>How many conditioning exposures per week: 3-5 depending on phase of year</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
         </is>
       </c>
     </row>
@@ -1893,9 +1965,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1908,10 +1980,14 @@
           <t>How many conditioning exposures per week: 3-5 depending on phase of year</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
         </is>
       </c>
     </row>
@@ -1938,12 +2014,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1956,10 +2032,14 @@
           <t>How many conditioning exposures per week: 3-5 depending on phase of year</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2084,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -2052,7 +2136,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -2100,7 +2188,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -2135,7 +2227,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2148,7 +2240,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -2183,7 +2279,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2196,7 +2292,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -2231,7 +2331,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2244,7 +2344,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -2279,7 +2383,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2292,10 +2396,14 @@
           <t>How many hard days per week max: 4</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 states a hard-day max of 4.</t>
+          <t>RULED and amended into Bible S2: prefer 4 hard days, permit 5, unit is DAYS. Doubling up is ONE hard day and two hard sessions, free against the budget. Easy/long-slow never counts. A 6th hard day is refused with plain copy. Bye-recovery and early off-season keep the lower 2/4.</t>
         </is>
       </c>
     </row>
@@ -2325,9 +2433,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>bible_conflict</t>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2340,10 +2448,14 @@
           <t>How many hard days per week max: 4</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 states a hard-DAY max of 4. This permits 5. Also the unit question: the Bible counts DAYS ("6 sessions ... spread over 3-4 days"), the engine spends this on SESSIONS. Batch 3 owns the unit; this cell owns the number.</t>
+          <t>RULED and amended into Bible S2: prefer 4 hard days, permit 5, unit is DAYS. Doubling up is ONE hard day and two hard sessions, free against the budget. Easy/long-slow never counts. A 6th hard day is refused with plain copy. Bye-recovery and early off-season keep the lower 2/4.</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2500,11 @@
           <t>you can have 2-4 strength days (depending on preference and availability)</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -2436,7 +2552,11 @@
           <t>you can have 2-4 strength days (depending on preference and availability)</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -2484,7 +2604,11 @@
           <t>you can have 2-4 strength days (depending on preference and availability)</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -2532,7 +2656,11 @@
           <t>How many conditioning exposures per week: 3-5 depending on phase of year</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Bible S2 allows a bye to be "a really good time to rest and recover".</t>
@@ -2580,7 +2708,11 @@
           <t>How many conditioning exposures per week: 3-5 depending on phase of year</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Bible S2 allows a bye to be "a really good time to rest and recover".</t>
@@ -2628,7 +2760,11 @@
           <t>How many conditioning exposures per week: 3-5 depending on phase of year</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Value is an expression, not a literal — it varies with the athlete's anchors. Ruling it means ruling the EXPRESSION, or replacing it with a fixed number.</t>
@@ -2676,7 +2812,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -2724,7 +2864,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -2772,7 +2916,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -2807,7 +2955,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2820,7 +2968,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -2855,7 +3007,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2868,7 +3020,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -2901,9 +3057,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>bible_conflict</t>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2916,10 +3072,14 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 says 1-2 days fully off each week. This allows 3.</t>
+          <t>RULED and amended into Bible S2: 3 full rest days are permitted in bye-recovery weeks and early off-season only. Elsewhere 1-2 stands.</t>
         </is>
       </c>
     </row>
@@ -2951,7 +3111,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2964,10 +3124,14 @@
           <t>How many hard days per week max: 4</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 states a hard-day max of 4.</t>
+          <t>RULED and amended into Bible S2: prefer 4 hard days, permit 5, unit is DAYS. Doubling up is ONE hard day and two hard sessions, free against the budget. Easy/long-slow never counts. A 6th hard day is refused with plain copy. Bye-recovery and early off-season keep the lower 2/4.</t>
         </is>
       </c>
     </row>
@@ -2999,7 +3163,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3012,10 +3176,14 @@
           <t>How many hard days per week max: 4</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 states a hard-day max of 4.</t>
+          <t>RULED and amended into Bible S2: prefer 4 hard days, permit 5, unit is DAYS. Doubling up is ONE hard day and two hard sessions, free against the budget. Easy/long-slow never counts. A 6th hard day is refused with plain copy. Bye-recovery and early off-season keep the lower 2/4.</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3228,11 @@
           <t>up to 4 strengths pluys recovery mobility gunshow if wanted</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
           <t>Bible S1: weeks 1-2 optional, "zero completed sessions is a valid honest week".</t>
@@ -3090,7 +3262,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -3108,7 +3280,11 @@
           <t>up to 4 strengths pluys recovery mobility gunshow if wanted</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -3156,7 +3332,11 @@
           <t>up to 4 strengths pluys recovery mobility gunshow if wanted</t>
         </is>
       </c>
-      <c r="I46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -3204,7 +3384,11 @@
           <t>3-5 conditioning</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
           <t>Bible S1: off-season weeks 1-2 are the OPTIONAL block, nothing compulsory.</t>
@@ -3252,7 +3436,11 @@
           <t>3-5 conditioning</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
           <t>Bible S1: off-season weeks 1-2 are the OPTIONAL block, nothing compulsory.</t>
@@ -3300,7 +3488,11 @@
           <t>3-5 conditioning</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
           <t>Bible S1: off-season weeks 1-2 are the OPTIONAL block, nothing compulsory.</t>
@@ -3348,7 +3540,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
           <t>Bible S2 exempts early off-season from the floor of 1.</t>
@@ -3396,7 +3592,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
           <t>Bible S2 exempts early off-season from the floor of 1.</t>
@@ -3444,7 +3644,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
           <t>Bible S2 exempts early off-season from the floor of 1.</t>
@@ -3479,7 +3683,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3492,7 +3696,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -3527,7 +3735,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3540,7 +3748,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -3573,9 +3785,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>bible_conflict</t>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -3588,10 +3800,14 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 says 1-2 days fully off each week. This allows 3.</t>
+          <t>RULED and amended into Bible S2: 3 full rest days are permitted in bye-recovery weeks and early off-season only. Elsewhere 1-2 stands.</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3839,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3636,10 +3852,14 @@
           <t>How many hard days per week max: 4</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 states a hard-day max of 4.</t>
+          <t>RULED and amended into Bible S2: prefer 4 hard days, permit 5, unit is DAYS. Doubling up is ONE hard day and two hard sessions, free against the budget. Easy/long-slow never counts. A 6th hard day is refused with plain copy. Bye-recovery and early off-season keep the lower 2/4.</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3891,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3684,10 +3904,14 @@
           <t>How many hard days per week max: 4</t>
         </is>
       </c>
-      <c r="I57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 states a hard-day max of 4.</t>
+          <t>RULED and amended into Bible S2: prefer 4 hard days, permit 5, unit is DAYS. Doubling up is ONE hard day and two hard sessions, free against the budget. Easy/long-slow never counts. A 6th hard day is refused with plain copy. Bye-recovery and early off-season keep the lower 2/4.</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3956,11 @@
           <t>up to 4 strengths pluys recovery mobility gunshow if wanted</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -3780,7 +4008,11 @@
           <t>up to 4 strengths pluys recovery mobility gunshow if wanted</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -3828,7 +4060,11 @@
           <t>up to 4 strengths pluys recovery mobility gunshow if wanted</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -3861,9 +4097,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3876,10 +4112,14 @@
           <t>3-5 conditioning</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr"/>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
         </is>
       </c>
     </row>
@@ -3909,9 +4149,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3924,10 +4164,14 @@
           <t>3-5 conditioning</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
         </is>
       </c>
     </row>
@@ -3957,9 +4201,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3972,10 +4216,14 @@
           <t>3-5 conditioning</t>
         </is>
       </c>
-      <c r="I63" s="4" t="inlineStr"/>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4268,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr"/>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -4068,7 +4320,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr"/>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -4116,7 +4372,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -4151,7 +4411,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -4164,7 +4424,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I67" s="4" t="inlineStr"/>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -4199,7 +4463,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -4212,7 +4476,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr"/>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -4247,7 +4515,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -4260,7 +4528,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr"/>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -4295,7 +4567,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -4308,10 +4580,14 @@
           <t>How many hard days per week max: 4</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 states a hard-day max of 4.</t>
+          <t>RULED and amended into Bible S2: prefer 4 hard days, permit 5, unit is DAYS. Doubling up is ONE hard day and two hard sessions, free against the budget. Easy/long-slow never counts. A 6th hard day is refused with plain copy. Bye-recovery and early off-season keep the lower 2/4.</t>
         </is>
       </c>
     </row>
@@ -4341,9 +4617,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>bible_conflict</t>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -4356,10 +4632,14 @@
           <t>How many hard days per week max: 4</t>
         </is>
       </c>
-      <c r="I71" s="4" t="inlineStr"/>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 states a hard-DAY max of 4. This permits 5. Also the unit question: the Bible counts DAYS ("6 sessions ... spread over 3-4 days"), the engine spends this on SESSIONS. Batch 3 owns the unit; this cell owns the number.</t>
+          <t>RULED and amended into Bible S2: prefer 4 hard days, permit 5, unit is DAYS. Doubling up is ONE hard day and two hard sessions, free against the budget. Easy/long-slow never counts. A 6th hard day is refused with plain copy. Bye-recovery and early off-season keep the lower 2/4.</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4684,11 @@
           <t>up to 4 strengths pluys recovery mobility gunshow if wanted</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -4452,7 +4736,11 @@
           <t>up to 4 strengths pluys recovery mobility gunshow if wanted</t>
         </is>
       </c>
-      <c r="I73" s="4" t="inlineStr"/>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -4500,7 +4788,11 @@
           <t>up to 4 strengths pluys recovery mobility gunshow if wanted</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -4533,9 +4825,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -4548,10 +4840,14 @@
           <t>3-5 conditioning</t>
         </is>
       </c>
-      <c r="I75" s="4" t="inlineStr"/>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
         </is>
       </c>
     </row>
@@ -4581,9 +4877,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -4596,10 +4892,14 @@
           <t>3-5 conditioning</t>
         </is>
       </c>
-      <c r="I76" s="4" t="inlineStr"/>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
         </is>
       </c>
     </row>
@@ -4629,9 +4929,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -4644,10 +4944,14 @@
           <t>3-5 conditioning</t>
         </is>
       </c>
-      <c r="I77" s="4" t="inlineStr"/>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4996,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr"/>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -4740,7 +5048,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I79" s="4" t="inlineStr"/>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -4788,7 +5100,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -4823,7 +5139,7 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4836,7 +5152,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I81" s="4" t="inlineStr"/>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -4871,7 +5191,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4884,7 +5204,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr"/>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -4919,7 +5243,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -4932,7 +5256,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -4967,7 +5295,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4980,10 +5308,14 @@
           <t>How many hard days per week max: 4</t>
         </is>
       </c>
-      <c r="I84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 states a hard-day max of 4.</t>
+          <t>RULED and amended into Bible S2: prefer 4 hard days, permit 5, unit is DAYS. Doubling up is ONE hard day and two hard sessions, free against the budget. Easy/long-slow never counts. A 6th hard day is refused with plain copy. Bye-recovery and early off-season keep the lower 2/4.</t>
         </is>
       </c>
     </row>
@@ -5013,9 +5345,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr">
-        <is>
-          <t>bible_conflict</t>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -5028,17 +5360,21 @@
           <t>How many hard days per week max: 4</t>
         </is>
       </c>
-      <c r="I85" s="4" t="inlineStr"/>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 states a hard-DAY max of 4. This permits 5. Also the unit question: the Bible counts DAYS ("6 sessions ... spread over 3-4 days"), the engine spends this on SESSIONS. Batch 3 owns the unit; this cell owns the number.</t>
+          <t>RULED and amended into Bible S2: prefer 4 hard days, permit 5, unit is DAYS. Doubling up is ONE hard day and two hard sessions, free against the budget. Easy/long-slow never counts. A 6th hard day is refused with plain copy. Bye-recovery and early off-season keep the lower 2/4.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5076,7 +5412,11 @@
           <t>2-4 strength - again double ups are good</t>
         </is>
       </c>
-      <c r="I86" s="4" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -5086,7 +5426,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5124,7 +5464,11 @@
           <t>2-4 strength - again double ups are good</t>
         </is>
       </c>
-      <c r="I87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -5134,7 +5478,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5172,7 +5516,11 @@
           <t>2-4 strength - again double ups are good</t>
         </is>
       </c>
-      <c r="I88" s="4" t="inlineStr"/>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
           <t>Within the Bible's 2-4 strength days for this phase.</t>
@@ -5182,7 +5530,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5205,9 +5553,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -5220,17 +5568,21 @@
           <t>1-3 extra conditioning depending on team training</t>
         </is>
       </c>
-      <c r="I89" s="4" t="inlineStr"/>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5253,9 +5605,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -5268,17 +5620,21 @@
           <t>1-3 extra conditioning depending on team training</t>
         </is>
       </c>
-      <c r="I90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5301,9 +5657,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -5316,17 +5672,21 @@
           <t>1-3 extra conditioning depending on team training</t>
         </is>
       </c>
-      <c r="I91" s="4" t="inlineStr"/>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5364,7 +5724,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I92" s="4" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -5374,7 +5738,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5412,7 +5776,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I93" s="4" t="inlineStr"/>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -5422,7 +5790,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5460,7 +5828,11 @@
           <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
         </is>
       </c>
-      <c r="I94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
           <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
@@ -5470,7 +5842,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5495,7 +5867,7 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -5508,7 +5880,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -5518,7 +5894,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5543,7 +5919,7 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -5556,7 +5932,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -5566,7 +5946,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5591,7 +5971,7 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -5604,7 +5984,11 @@
           <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
         </is>
       </c>
-      <c r="I97" s="4" t="inlineStr"/>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
           <t>Bible S2: 1-2 days fully off each week.</t>
@@ -5614,7 +5998,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5639,7 +6023,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>bible_range</t>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -5652,17 +6036,21 @@
           <t>How many hard days per week max: 4</t>
         </is>
       </c>
-      <c r="I98" s="4" t="inlineStr"/>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 states a hard-day max of 4.</t>
+          <t>RULED and amended into Bible S2: prefer 4 hard days, permit 5, unit is DAYS. Doubling up is ONE hard day and two hard sessions, free against the budget. Easy/long-slow never counts. A 6th hard day is refused with plain copy. Bye-recovery and early off-season keep the lower 2/4.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5685,9 +6073,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>bible_conflict</t>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>bible_anchor</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -5700,1354 +6088,14 @@
           <t>How many hard days per week max: 4</t>
         </is>
       </c>
-      <c r="I99" s="4" t="inlineStr"/>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 states a hard-DAY max of 4. This permits 5. Also the unit question: the Bible counts DAYS ("6 sessions ... spread over 3-4 days"), the engine spends this on SESSIONS. Batch 3 owns the unit; this cell owns the number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>strength</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>2-4 strength - again double ups are good</t>
-        </is>
-      </c>
-      <c r="I100" s="4" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>Within the Bible's 2-4 strength days for this phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>strength</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>preferredMin</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>2-4 strength - again double ups are good</t>
-        </is>
-      </c>
-      <c r="I101" s="4" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>Within the Bible's 2-4 strength days for this phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>strength</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>preferredMax</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>2-4 strength - again double ups are good</t>
-        </is>
-      </c>
-      <c r="I102" s="4" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>Within the Bible's 2-4 strength days for this phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>conditioning</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F103" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>1-3 extra conditioning depending on team training</t>
-        </is>
-      </c>
-      <c r="I103" s="4" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>conditioning</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>preferredMin</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F104" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>1-3 extra conditioning depending on team training</t>
-        </is>
-      </c>
-      <c r="I104" s="4" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>conditioning</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>preferredMax</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F105" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>1-3 extra conditioning depending on team training</t>
-        </is>
-      </c>
-      <c r="I105" s="4" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>sprintCod</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
-        </is>
-      </c>
-      <c r="I106" s="4" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>sprintCod</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>preferredMin</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
-        </is>
-      </c>
-      <c r="I107" s="4" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>sprintCod</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>preferredMax</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
-        </is>
-      </c>
-      <c r="I108" s="4" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>fullRest</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
-        </is>
-      </c>
-      <c r="I109" s="4" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2: 1-2 days fully off each week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>fullRest</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>preferredMin</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
-        </is>
-      </c>
-      <c r="I110" s="4" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2: 1-2 days fully off each week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>fullRest</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>preferredMax</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2: 1-2 days fully off each week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>hardDays</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>preferred</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>How many hard days per week max: 4</t>
-        </is>
-      </c>
-      <c r="I112" s="4" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2 states a hard-day max of 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>hardDays</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>permitted</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="inlineStr">
-        <is>
-          <t>bible_conflict</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>How many hard days per week max: 4</t>
-        </is>
-      </c>
-      <c r="I113" s="4" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2 states a hard-DAY max of 4. This permits 5. Also the unit question: the Bible counts DAYS ("6 sessions ... spread over 3-4 days"), the engine spends this on SESSIONS. Batch 3 owns the unit; this cell owns the number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>strength</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>2-4 strength - again double ups are good</t>
-        </is>
-      </c>
-      <c r="I114" s="4" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>Within the Bible's 2-4 strength days for this phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>strength</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>preferredMin</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>2-4 strength - again double ups are good</t>
-        </is>
-      </c>
-      <c r="I115" s="4" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>Within the Bible's 2-4 strength days for this phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>strength</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>preferredMax</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>2-4 strength - again double ups are good</t>
-        </is>
-      </c>
-      <c r="I116" s="4" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>Within the Bible's 2-4 strength days for this phase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>conditioning</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F117" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>1-3 extra conditioning depending on team training</t>
-        </is>
-      </c>
-      <c r="I117" s="4" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>conditioning</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>preferredMin</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>1-3 extra conditioning depending on team training</t>
-        </is>
-      </c>
-      <c r="I118" s="4" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>conditioning</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>preferredMax</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F119" s="8" t="inlineStr">
-        <is>
-          <t>bible_ambiguous</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>1-3 extra conditioning depending on team training</t>
-        </is>
-      </c>
-      <c r="I119" s="4" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>Two Bible lines give different BASES: S2 says 3-5 conditioning exposures TOTAL (team training and games included), S3 says 1-3 EXTRA conditioning. Which base this cell counts in is unruled, so neither line can confirm or refute it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>sprintCod</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
-        </is>
-      </c>
-      <c r="I120" s="4" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>sprintCod</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>preferredMin</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
-        </is>
-      </c>
-      <c r="I121" s="4" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>sprintCod</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>preferredMax</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>the year-round required minimum is 1 genuine sprint/high-speed exposure per week except early off-season</t>
-        </is>
-      </c>
-      <c r="I122" s="4" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>fullRest</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
-        </is>
-      </c>
-      <c r="I123" s="4" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2: 1-2 days fully off each week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>fullRest</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>preferredMin</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
-        </is>
-      </c>
-      <c r="I124" s="4" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2: 1-2 days fully off each week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>fullRest</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>preferredMax</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>I'd almost prefer it so give them 1-2 days fully off each week</t>
-        </is>
-      </c>
-      <c r="I125" s="4" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2: 1-2 days fully off each week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>hardDays</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>preferred</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>bible_range</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>How many hard days per week max: 4</t>
-        </is>
-      </c>
-      <c r="I126" s="4" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2 states a hard-day max of 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>hardDays</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>permitted</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F127" s="7" t="inlineStr">
-        <is>
-          <t>bible_conflict</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>How many hard days per week max: 4</t>
-        </is>
-      </c>
-      <c r="I127" s="4" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>Bible S2 states a hard-DAY max of 4. This permits 5. Also the unit question: the Bible counts DAYS ("6 sessions ... spread over 3-4 days"), the engine spends this on SESSIONS. Batch 3 owns the unit; this cell owns the number.</t>
+          <t>RULED and amended into Bible S2: prefer 4 hard days, permit 5, unit is DAYS. Doubling up is ONE hard day and two hard sessions, free against the budget. Easy/long-slow never counts. A 6th hard day is refused with plain copy. Bye-recovery and early off-season keep the lower 2/4.</t>
         </is>
       </c>
     </row>
@@ -7062,7 +6110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7132,7 +6180,7 @@
           <t>3 (engine floor)</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -7165,7 +6213,7 @@
           <t>5 (engine floors, in-season + pre-season only)</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -7264,7 +6312,7 @@
           <t>+1</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -7297,7 +6345,7 @@
           <t>readiness-conditioned (1/2/2) — FORBIDDEN by the ruling</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>ruling_violation</t>
         </is>
@@ -7330,7 +6378,7 @@
           <t>availableDays - core - optional (derived, unauthored)</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -7396,7 +6444,7 @@
           <t>5 (engine floors, in-season + pre-season only)</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -7495,7 +6543,7 @@
           <t>+1</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -7528,7 +6576,7 @@
           <t>readiness-conditioned (1/2/2) — FORBIDDEN by the ruling</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>ruling_violation</t>
         </is>
@@ -7561,7 +6609,7 @@
           <t>availableDays - core - optional (derived, unauthored)</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -7627,7 +6675,7 @@
           <t>5 (engine floors, in-season + pre-season only)</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -7726,7 +6774,7 @@
           <t>+1</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -7759,7 +6807,7 @@
           <t>readiness-conditioned (1/2/2) — FORBIDDEN by the ruling</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>ruling_violation</t>
         </is>
@@ -7792,7 +6840,7 @@
           <t>availableDays - core - optional (derived, unauthored)</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -7858,7 +6906,7 @@
           <t>5 (engine floors, in-season + pre-season only)</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -7924,7 +6972,7 @@
           <t>2 (else 3)</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -7990,7 +7038,7 @@
           <t>readiness-conditioned (1/2/2) — FORBIDDEN by the ruling</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>ruling_violation</t>
         </is>
@@ -8023,7 +7071,7 @@
           <t>availableDays - core - optional (derived, unauthored)</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -8089,7 +7137,7 @@
           <t>5 (engine floors, in-season + pre-season only)</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -8221,7 +7269,7 @@
           <t>readiness-conditioned (1/2/2) — FORBIDDEN by the ruling</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>ruling_violation</t>
         </is>
@@ -8254,7 +7302,7 @@
           <t>availableDays - core - optional (derived, unauthored)</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -8320,7 +7368,7 @@
           <t>5 (engine floors, in-season + pre-season only)</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -8452,7 +7500,7 @@
           <t>readiness-conditioned (1/2/2) — FORBIDDEN by the ruling</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>ruling_violation</t>
         </is>
@@ -8485,7 +7533,7 @@
           <t>availableDays - core - optional (derived, unauthored)</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -8500,7 +7548,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -8515,12 +7563,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>4 no-game / 3 game (engine floors)</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>engine_behaviour_to_migrate</t>
+          <t>none — this mode has no behaviour here today</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>silent_today</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
@@ -8533,7 +7581,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -8551,7 +7599,7 @@
           <t>5 (engine floors, in-season + pre-season only)</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
@@ -8566,7 +7614,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -8599,7 +7647,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -8632,7 +7680,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -8665,7 +7713,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -8683,7 +7731,7 @@
           <t>readiness-conditioned (1/2/2) — FORBIDDEN by the ruling</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>ruling_violation</t>
         </is>
@@ -8698,7 +7746,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>early_preseason</t>
+          <t>preseason</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -8716,475 +7764,13 @@
           <t>availableDays - core - optional (derived, unauthored)</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>engine_behaviour_to_migrate</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Engine derives this as availableDays - core - optional. Never authored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>strengthTargetWithTwoOrMoreTeamDays</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>4 no-game / 3 game (engine floors)</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>engine_behaviour_to_migrate</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Gym work layered onto an already-hard team day is not a new hard day. This is the behaviour all three deleted engine floors encoded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>minimumAvailableDaysForPreferredTarget</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>5 (engine floors, in-season + pre-season only)</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>engine_behaviour_to_migrate</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>All three engine floors used &gt;= 5. Nothing states why 5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>strengthTargetBelowThatAvailability</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>none — this mode has no behaviour here today</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>silent_today</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Today this is an implicit fall-through, never stated anywhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>targetAtOrBelowThreeAvailableDays</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>none — this mode has no behaviour here today</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>silent_today</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Only early off-season has this today (2 vs 3). Every other mode is silent — which is absence rendered as approval, not a decision that low availability changes nothing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>moderateStrengthAllowance</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>none — this mode has no behaviour here today</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>silent_today</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>The G-2 upper session is core but low-fatigue. Engine adds +1 in-season only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>optionalSessionCap</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>readiness-conditioned (1/2/2) — FORBIDDEN by the ruling</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>ruling_violation</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Engine caps this by READINESS today (low 1 / medium 2 / high 2), which the ruling forbids. Needs a schedule-conditioned value instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>mid_preseason</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>recoverySessionCap</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>availableDays - core - optional (derived, unauthored)</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>engine_behaviour_to_migrate</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Engine derives this as availableDays - core - optional. Never authored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>strengthTargetWithTwoOrMoreTeamDays</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>4 no-game / 3 game (engine floors)</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>engine_behaviour_to_migrate</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Gym work layered onto an already-hard team day is not a new hard day. This is the behaviour all three deleted engine floors encoded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>minimumAvailableDaysForPreferredTarget</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>5 (engine floors, in-season + pre-season only)</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>engine_behaviour_to_migrate</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>All three engine floors used &gt;= 5. Nothing states why 5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>strengthTargetBelowThatAvailability</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>none — this mode has no behaviour here today</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>silent_today</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Today this is an implicit fall-through, never stated anywhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>targetAtOrBelowThreeAvailableDays</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>none — this mode has no behaviour here today</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>silent_today</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Only early off-season has this today (2 vs 3). Every other mode is silent — which is absence rendered as approval, not a decision that low availability changes nothing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>moderateStrengthAllowance</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>none — this mode has no behaviour here today</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>silent_today</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>The G-2 upper session is core but low-fatigue. Engine adds +1 in-season only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>optionalSessionCap</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>readiness-conditioned (1/2/2) — FORBIDDEN by the ruling</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>ruling_violation</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Engine caps this by READINESS today (low 1 / medium 2 / high 2), which the ruling forbids. Needs a schedule-conditioned value instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>late_preseason</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Pre-season</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>recoverySessionCap</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>availableDays - core - optional (derived, unauthored)</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>engine_behaviour_to_migrate</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>Engine derives this as availableDays - core - optional. Never authored.</t>
         </is>

--- a/docs/EXPOSURE_CONTRACT_REVIEW_2026-07-28.xlsx
+++ b/docs/EXPOSURE_CONTRACT_REVIEW_2026-07-28.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -566,138 +566,222 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>THE TABS</t>
+          <t>THE PRACTICE-MATCH RULING (Sam, 2026-07-28)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Contract V2 first cells  - 3 cells. AUTHOR THESE FIRST (ruling 1).</t>
+          <t>"A pre-season practice-match week is structurally an IN-SEASON GAME WEEK - same shape,</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Base numbers             - 126 cells. 9 modes x 14 slots.</t>
+          <t>2 team trainings + 1 game - and carries the game week's authored numbers, not the</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Schedule columns         - 63 cells. 9 modes x 7 schedule-conditioned behaviours.</t>
+          <t>generic pre-season row."</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Open questions           - 4 questions that change what the cells mean.</t>
+          <t>So this workbook has NO practice-match row, and does not need one. A pre-season week</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Base + schedule = 189 authored cells. The 3 on tab 2 come first and are extra.</t>
+          <t>with a fixture reads the in_season_game_week row above; a pre-season week without one</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>HOW TO READ A ROW</t>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>reads the preseason row. The week keeps its pre-season identity either way - the ruling</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CURRENT VALUE  what ships today. Not evidence that anyone chose it.</t>
+          <t>is about the NUMBERS, not about where the week sits in the season.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAG           bible_range = inside a stated range. bible_conflict = outside one.</t>
+          <t>What it replaced: the builder took its selected target from the practice-match policy</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 bible_ambiguous = two Bible lines disagree on the base being counted.</t>
+          <t>and its preferred range from the pre-season row, so one contract declared a target of 3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 no_bible = nothing states it. derived_not_literal = an expression.</t>
+          <t>beside an aim of 4. Like strongByeBuild, the ruling was a DELETION - the game-week row</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BIBLE          the section and the sentence fragment, so a claim can be checked.</t>
+          <t>already said it, and the second row was the defect.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  RULED VALUE    blank. Sam fills this, or confirms the current value explicitly.</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>THE TABS</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>A BLANK RULED VALUE IS NOT APPROVAL</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Contract V2 first cells  - 3 cells. AUTHOR THESE FIRST (ruling 1).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>This is the defect the whole provenance unit keeps finding: an empty list read as a</t>
+          <t xml:space="preserve">  3. Base numbers             - 126 cells. 9 modes x 14 slots.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>completed review. Confirming a current value is a RULING and must be said out loud.</t>
+          <t xml:space="preserve">  4. Schedule columns         - 63 cells. 9 modes x 7 schedule-conditioned behaviours.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>WHAT THIS SHEET DOES NOT AUTHOR</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Open questions           - 4 questions that change what the cells mean.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>phaseWeek and the week-counting mechanism. Sam ruled subphase derives from two anchor</t>
+          <t xml:space="preserve">  Base + schedule = 189 authored cells. The 3 on tab 2 come first and are extra.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>dates per season, never a fixed week count, so the INPUT that selects a mode is due to</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>HOW TO READ A ROW</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CURRENT VALUE  what ships today. Not evidence that anyone chose it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FLAG           bible_range = inside a stated range. bible_conflict = outside one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 bible_ambiguous = two Bible lines disagree on the base being counted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 no_bible = nothing states it. derived_not_literal = an expression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BIBLE          the section and the sentence fragment, so a claim can be checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RULED VALUE    blank. Sam fills this, or confirms the current value explicitly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>A BLANK RULED VALUE IS NOT APPROVAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>This is the defect the whole provenance unit keeps finding: an empty list read as a</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>completed review. Confirming a current value is a RULING and must be said out loud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>WHAT THIS SHEET DOES NOT AUTHOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>phaseWeek and the week-counting mechanism. Sam ruled subphase derives from two anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>dates per season, never a fixed week count, so the INPUT that selects a mode is due to</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>change. This sheet authors the VALUES a mode carries, not how the mode is selected.</t>
         </is>
@@ -1051,7 +1135,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Within the Bible's 2-4 strength days for this phase.</t>
+          <t>Within the Bible's 2-4 strength days for this phase. ALSO GOVERNS the pre-season practice-match week (Sam, 2026-07-28): a fixture week is structurally a game week and carries this row.</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1187,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Within the Bible's 2-4 strength days for this phase.</t>
+          <t>Within the Bible's 2-4 strength days for this phase. ALSO GOVERNS the pre-season practice-match week (Sam, 2026-07-28): a fixture week is structurally a game week and carries this row.</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1239,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Within the Bible's 2-4 strength days for this phase.</t>
+          <t>Within the Bible's 2-4 strength days for this phase. ALSO GOVERNS the pre-season practice-match week (Sam, 2026-07-28): a fixture week is structurally a game week and carries this row.</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1291,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Value is an expression, not a literal — it varies with the athlete's anchors. Ruling it means ruling the EXPRESSION, or replacing it with a fixed number.</t>
+          <t>Value is an expression, not a literal — it varies with the athlete's anchors. Ruling it means ruling the EXPRESSION, or replacing it with a fixed number. ALSO GOVERNS the pre-season practice-match week (Sam, 2026-07-28): a fixture week is structurally a game week and carries this row.</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1343,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Value is an expression, not a literal — it varies with the athlete's anchors. Ruling it means ruling the EXPRESSION, or replacing it with a fixed number.</t>
+          <t>Value is an expression, not a literal — it varies with the athlete's anchors. Ruling it means ruling the EXPRESSION, or replacing it with a fixed number. ALSO GOVERNS the pre-season practice-match week (Sam, 2026-07-28): a fixture week is structurally a game week and carries this row.</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1395,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Value is an expression, not a literal — it varies with the athlete's anchors. Ruling it means ruling the EXPRESSION, or replacing it with a fixed number.</t>
+          <t>Value is an expression, not a literal — it varies with the athlete's anchors. Ruling it means ruling the EXPRESSION, or replacing it with a fixed number. ALSO GOVERNS the pre-season practice-match week (Sam, 2026-07-28): a fixture week is structurally a game week and carries this row.</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1447,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
+          <t>Bible S2 floor is 1; 2-3 is the usual maximum. ALSO GOVERNS the pre-season practice-match week (Sam, 2026-07-28): a fixture week is structurally a game week and carries this row.</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1499,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
+          <t>Bible S2 floor is 1; 2-3 is the usual maximum. ALSO GOVERNS the pre-season practice-match week (Sam, 2026-07-28): a fixture week is structurally a game week and carries this row.</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1551,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
+          <t>Bible S2 floor is 1; 2-3 is the usual maximum. ALSO GOVERNS the pre-season practice-match week (Sam, 2026-07-28): a fixture week is structurally a game week and carries this row.</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1603,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Bible S2: 1-2 days fully off each week.</t>
+          <t>Bible S2: 1-2 days fully off each week. ALSO GOVERNS the pre-season practice-match week (Sam, 2026-07-28): a fixture week is structurally a game week and carries this row.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1655,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Bible S2: 1-2 days fully off each week.</t>
+          <t>Bible S2: 1-2 days fully off each week. ALSO GOVERNS the pre-season practice-match week (Sam, 2026-07-28): a fixture week is structurally a game week and carries this row.</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1707,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Bible S2: 1-2 days fully off each week.</t>
+          <t>Bible S2: 1-2 days fully off each week. ALSO GOVERNS the pre-season practice-match week (Sam, 2026-07-28): a fixture week is structurally a game week and carries this row.</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5503,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Within the Bible's 2-4 strength days for this phase.</t>
+          <t>Within the Bible's 2-4 strength days for this phase. Applies to pre-season weeks WITHOUT a fixture. A pre-season practice-match week takes the in_season_game_week row instead (Sam, 2026-07-28).</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5555,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Within the Bible's 2-4 strength days for this phase.</t>
+          <t>Within the Bible's 2-4 strength days for this phase. Applies to pre-season weeks WITHOUT a fixture. A pre-season practice-match week takes the in_season_game_week row instead (Sam, 2026-07-28).</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5607,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Within the Bible's 2-4 strength days for this phase.</t>
+          <t>Within the Bible's 2-4 strength days for this phase. Applies to pre-season weeks WITHOUT a fixture. A pre-season practice-match week takes the in_season_game_week row instead (Sam, 2026-07-28).</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5659,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget. Applies to pre-season weeks WITHOUT a fixture. A pre-season practice-match week takes the in_season_game_week row instead (Sam, 2026-07-28).</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5711,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget. Applies to pre-season weeks WITHOUT a fixture. A pre-season practice-match week takes the in_season_game_week row instead (Sam, 2026-07-28).</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5763,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
+          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget. Applies to pre-season weeks WITHOUT a fixture. A pre-season practice-match week takes the in_season_game_week row instead (Sam, 2026-07-28).</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5815,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
+          <t>Bible S2 floor is 1; 2-3 is the usual maximum. Applies to pre-season weeks WITHOUT a fixture. A pre-season practice-match week takes the in_season_game_week row instead (Sam, 2026-07-28).</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5867,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
+          <t>Bible S2 floor is 1; 2-3 is the usual maximum. Applies to pre-season weeks WITHOUT a fixture. A pre-season practice-match week takes the in_season_game_week row instead (Sam, 2026-07-28).</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5919,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
+          <t>Bible S2 floor is 1; 2-3 is the usual maximum. Applies to pre-season weeks WITHOUT a fixture. A pre-season practice-match week takes the in_season_game_week row instead (Sam, 2026-07-28).</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5971,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Bible S2: 1-2 days fully off each week.</t>
+          <t>Bible S2: 1-2 days fully off each week. Applies to pre-season weeks WITHOUT a fixture. A pre-season practice-match week takes the in_season_game_week row instead (Sam, 2026-07-28).</t>
         </is>
       </c>
     </row>
@@ -5939,7 +6023,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Bible S2: 1-2 days fully off each week.</t>
+          <t>Bible S2: 1-2 days fully off each week. Applies to pre-season weeks WITHOUT a fixture. A pre-season practice-match week takes the in_season_game_week row instead (Sam, 2026-07-28).</t>
         </is>
       </c>
     </row>
@@ -5991,7 +6075,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Bible S2: 1-2 days fully off each week.</t>
+          <t>Bible S2: 1-2 days fully off each week. Applies to pre-season weeks WITHOUT a fixture. A pre-season practice-match week takes the in_season_game_week row instead (Sam, 2026-07-28).</t>
         </is>
       </c>
     </row>

--- a/docs/EXPOSURE_CONTRACT_REVIEW_2026-07-28.xlsx
+++ b/docs/EXPOSURE_CONTRACT_REVIEW_2026-07-28.xlsx
@@ -3470,12 +3470,12 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>RULED 2026-07-28</t>
+          <t>RULED 2026-09-07 (R-381)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Bible S1: off-season weeks 1-2 are the OPTIONAL block, nothing compulsory.</t>
+          <t>Preparation through week 4: optional light off-feet aerobic offers; no automatic speed. Shared OFFSEASON_PREPARATION policy.</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>RULED 2026-07-28</t>
+          <t>RULED 2026-09-07 (R-381)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Bible S1: off-season weeks 1-2 are the OPTIONAL block, nothing compulsory.</t>
+          <t>Preparation through week 4: optional light off-feet aerobic offers; no automatic speed. Shared OFFSEASON_PREPARATION policy.</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>RULED 2026-07-28</t>
+          <t>RULED 2026-09-07 (R-381)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Bible S1: off-season weeks 1-2 are the OPTIONAL block, nothing compulsory.</t>
+          <t>Preparation through week 4: optional light off-feet aerobic offers; no automatic speed. Shared OFFSEASON_PREPARATION policy.</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>RULED 2026-07-28</t>
+          <t>RULED 2026-09-07 (R-381)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
+          <t>Preparation through week 4: optional light off-feet aerobic offers; no automatic speed. Shared OFFSEASON_PREPARATION policy.</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>RULED 2026-07-28</t>
+          <t>RULED 2026-09-07 (R-381)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
+          <t>Preparation through week 4: optional light off-feet aerobic offers; no automatic speed. Shared OFFSEASON_PREPARATION policy.</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>RULED 2026-07-28</t>
+          <t>RULED 2026-09-07 (R-381)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>RULED: conditioning counts TOTAL, team training and games included. Weekly cap 5 TOTAL, in-season target 3, max 4 RUNNING sessions year-round, a 5th must be off-legs. S2 amended to state the basis and S3 annotated so its "extra" figures no longer read as a separate budget.</t>
+          <t>Preparation through week 4: optional light off-feet aerobic offers; no automatic speed. Shared OFFSEASON_PREPARATION policy.</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>RULED 2026-07-28</t>
+          <t>RULED 2026-09-07 (R-381)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
+          <t>Preparation through week 4: optional light off-feet aerobic offers; no automatic speed. Shared OFFSEASON_PREPARATION policy.</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>RULED 2026-07-28</t>
+          <t>RULED 2026-09-07 (R-381)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
+          <t>Preparation through week 4: optional light off-feet aerobic offers; no automatic speed. Shared OFFSEASON_PREPARATION policy.</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>RULED 2026-07-28</t>
+          <t>RULED 2026-09-07 (R-381)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Bible S2 floor is 1; 2-3 is the usual maximum.</t>
+          <t>Preparation through week 4: optional light off-feet aerobic offers; no automatic speed. Shared OFFSEASON_PREPARATION policy.</t>
         </is>
       </c>
     </row>
